--- a/samples/예시데이터_판매현황(26.07).xlsx
+++ b/samples/예시데이터_판매현황(26.07).xlsx
@@ -568,7 +568,7 @@
         <v>104000</v>
       </c>
       <c r="J5" t="str">
-        <v>예시협력사 A</v>
+        <v>예시중국공장(가상)</v>
       </c>
       <c r="K5" t="str">
         <v/>
